--- a/diagnostic/Business-Diagnostic-Rebuild.xlsx
+++ b/diagnostic/Business-Diagnostic-Rebuild.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Write the four option texts, in order best to worst. The line between option 2 and option 3 is the benchmark.</t>
+          <t>All 29 are drafted. Correct what is wrong in the PROPOSED column. The line between option 2 and option 3 is the benchmark.</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>YOUR OPTION</t>
+          <t>PROPOSED, mark it up</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
@@ -795,7 +795,11 @@
       <c r="G3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>It runs fine</t>
+        </is>
+      </c>
       <c r="I3" s="9" t="n">
         <v>0</v>
       </c>
@@ -819,7 +823,11 @@
       <c r="G4" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>It runs, but decisions pile up waiting for me</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="n">
         <v>33</v>
       </c>
@@ -843,7 +851,11 @@
       <c r="G5" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>It degrades quickly</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="n">
         <v>67</v>
       </c>
@@ -867,7 +879,11 @@
       <c r="G6" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>It stops</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="n">
         <v>100</v>
       </c>
@@ -937,7 +953,11 @@
       <c r="G10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>More than a day</t>
+        </is>
+      </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
       </c>
@@ -961,7 +981,11 @@
       <c r="G11" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Half a day</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="n">
         <v>33</v>
       </c>
@@ -985,7 +1009,11 @@
       <c r="G12" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>An hour or two</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n">
         <v>67</v>
       </c>
@@ -1009,7 +1037,11 @@
       <c r="G13" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>None of it</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="n">
         <v>100</v>
       </c>
@@ -1079,7 +1111,11 @@
       <c r="G17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="n">
         <v>0</v>
       </c>
@@ -1103,7 +1139,11 @@
       <c r="G18" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Once</t>
+        </is>
+      </c>
       <c r="I18" s="9" t="n">
         <v>33</v>
       </c>
@@ -1127,7 +1167,11 @@
       <c r="G19" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>A few times</t>
+        </is>
+      </c>
       <c r="I19" s="11" t="n">
         <v>67</v>
       </c>
@@ -1151,7 +1195,11 @@
       <c r="G20" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>That's the normal state</t>
+        </is>
+      </c>
       <c r="I20" s="11" t="n">
         <v>100</v>
       </c>
@@ -1221,7 +1269,11 @@
       <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Two or fewer</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
@@ -1245,7 +1297,11 @@
       <c r="G25" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Three to six</t>
+        </is>
+      </c>
       <c r="I25" s="9" t="n">
         <v>33</v>
       </c>
@@ -1269,7 +1325,11 @@
       <c r="G26" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Seven to twelve</t>
+        </is>
+      </c>
       <c r="I26" s="11" t="n">
         <v>67</v>
       </c>
@@ -1293,7 +1353,11 @@
       <c r="G27" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>More than twelve</t>
+        </is>
+      </c>
       <c r="I27" s="11" t="n">
         <v>100</v>
       </c>
@@ -1381,7 +1445,11 @@
       <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Under half full</t>
+        </is>
+      </c>
       <c r="I32" s="9" t="n">
         <v>0</v>
       </c>
@@ -1405,7 +1473,11 @@
       <c r="G33" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>About two thirds</t>
+        </is>
+      </c>
       <c r="I33" s="9" t="n">
         <v>33</v>
       </c>
@@ -1429,7 +1501,11 @@
       <c r="G34" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Full, or close to it</t>
+        </is>
+      </c>
       <c r="I34" s="11" t="n">
         <v>67</v>
       </c>
@@ -1453,7 +1529,11 @@
       <c r="G35" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Over capacity, we're behind</t>
+        </is>
+      </c>
       <c r="I35" s="11" t="n">
         <v>100</v>
       </c>
@@ -1541,7 +1621,11 @@
       <c r="G40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I40" s="9" t="n">
         <v>0</v>
       </c>
@@ -1565,7 +1649,11 @@
       <c r="G41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Once or twice</t>
+        </is>
+      </c>
       <c r="I41" s="9" t="n">
         <v>33</v>
       </c>
@@ -1589,7 +1677,11 @@
       <c r="G42" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Most months</t>
+        </is>
+      </c>
       <c r="I42" s="11" t="n">
         <v>67</v>
       </c>
@@ -1613,7 +1705,11 @@
       <c r="G43" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Constantly</t>
+        </is>
+      </c>
       <c r="I43" s="11" t="n">
         <v>100</v>
       </c>
@@ -1683,7 +1779,11 @@
       <c r="G47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Shorter</t>
+        </is>
+      </c>
       <c r="I47" s="9" t="n">
         <v>0</v>
       </c>
@@ -1707,7 +1807,11 @@
       <c r="G48" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>About the same</t>
+        </is>
+      </c>
       <c r="I48" s="9" t="n">
         <v>33</v>
       </c>
@@ -1731,7 +1835,11 @@
       <c r="G49" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Longer</t>
+        </is>
+      </c>
       <c r="I49" s="11" t="n">
         <v>67</v>
       </c>
@@ -1755,7 +1863,11 @@
       <c r="G50" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Much longer</t>
+        </is>
+      </c>
       <c r="I50" s="11" t="n">
         <v>100</v>
       </c>
@@ -1825,7 +1937,11 @@
       <c r="G54" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Comfortably ahead</t>
+        </is>
+      </c>
       <c r="I54" s="9" t="n">
         <v>0</v>
       </c>
@@ -1849,7 +1965,11 @@
       <c r="G55" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>A few days ahead</t>
+        </is>
+      </c>
       <c r="I55" s="9" t="n">
         <v>33</v>
       </c>
@@ -1873,7 +1993,11 @@
       <c r="G56" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>The day before</t>
+        </is>
+      </c>
       <c r="I56" s="11" t="n">
         <v>67</v>
       </c>
@@ -1897,7 +2021,11 @@
       <c r="G57" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>We're finishing it as it starts</t>
+        </is>
+      </c>
       <c r="I57" s="11" t="n">
         <v>100</v>
       </c>
@@ -1967,7 +2095,11 @@
       <c r="G61" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
@@ -1991,7 +2123,11 @@
       <c r="G62" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
       <c r="I62" s="9" t="n">
         <v>33</v>
       </c>
@@ -2015,7 +2151,11 @@
       <c r="G63" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Most weeks</t>
+        </is>
+      </c>
       <c r="I63" s="11" t="n">
         <v>67</v>
       </c>
@@ -2039,7 +2179,11 @@
       <c r="G64" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Constantly</t>
+        </is>
+      </c>
       <c r="I64" s="11" t="n">
         <v>100</v>
       </c>
@@ -2109,7 +2253,11 @@
       <c r="G68" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Most of them, over 70%</t>
+        </is>
+      </c>
       <c r="I68" s="9" t="n">
         <v>0</v>
       </c>
@@ -2133,7 +2281,11 @@
       <c r="G69" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>About half</t>
+        </is>
+      </c>
       <c r="I69" s="9" t="n">
         <v>33</v>
       </c>
@@ -2157,7 +2309,11 @@
       <c r="G70" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Under a third</t>
+        </is>
+      </c>
       <c r="I70" s="11" t="n">
         <v>67</v>
       </c>
@@ -2181,7 +2337,11 @@
       <c r="G71" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Almost none</t>
+        </is>
+      </c>
       <c r="I71" s="11" t="n">
         <v>100</v>
       </c>
@@ -2251,7 +2411,11 @@
       <c r="G75" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Nearly all of it</t>
+        </is>
+      </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
@@ -2275,7 +2439,11 @@
       <c r="G76" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>More than half</t>
+        </is>
+      </c>
       <c r="I76" s="9" t="n">
         <v>33</v>
       </c>
@@ -2299,7 +2467,11 @@
       <c r="G77" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>About half or less</t>
+        </is>
+      </c>
       <c r="I77" s="11" t="n">
         <v>67</v>
       </c>
@@ -2323,7 +2495,11 @@
       <c r="G78" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>A small slice, they spread it around</t>
+        </is>
+      </c>
       <c r="I78" s="11" t="n">
         <v>100</v>
       </c>
@@ -2411,7 +2587,11 @@
       <c r="G83" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Usually</t>
+        </is>
+      </c>
       <c r="I83" s="9" t="n">
         <v>0</v>
       </c>
@@ -2435,7 +2615,11 @@
       <c r="G84" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
       <c r="I84" s="9" t="n">
         <v>33</v>
       </c>
@@ -2459,7 +2643,11 @@
       <c r="G85" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
       <c r="I85" s="11" t="n">
         <v>67</v>
       </c>
@@ -2483,7 +2671,11 @@
       <c r="G86" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
       <c r="I86" s="11" t="n">
         <v>100</v>
       </c>
@@ -2553,7 +2745,11 @@
       <c r="G90" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Most of them</t>
+        </is>
+      </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
@@ -2577,7 +2773,11 @@
       <c r="G91" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>About half</t>
+        </is>
+      </c>
       <c r="I91" s="9" t="n">
         <v>33</v>
       </c>
@@ -2601,7 +2801,11 @@
       <c r="G92" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>A few</t>
+        </is>
+      </c>
       <c r="I92" s="11" t="n">
         <v>67</v>
       </c>
@@ -2625,7 +2829,11 @@
       <c r="G93" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Almost none</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="n">
         <v>100</v>
       </c>
@@ -2695,7 +2903,11 @@
       <c r="G97" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Almost none</t>
+        </is>
+      </c>
       <c r="I97" s="9" t="n">
         <v>0</v>
       </c>
@@ -2719,7 +2931,11 @@
       <c r="G98" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>A handful</t>
+        </is>
+      </c>
       <c r="I98" s="9" t="n">
         <v>33</v>
       </c>
@@ -2743,7 +2959,11 @@
       <c r="G99" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>A steady stream</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="n">
         <v>67</v>
       </c>
@@ -2767,7 +2987,11 @@
       <c r="G100" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Most of them</t>
+        </is>
+      </c>
       <c r="I100" s="11" t="n">
         <v>100</v>
       </c>
@@ -2837,7 +3061,11 @@
       <c r="G104" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Yes, we ask every one and we know</t>
+        </is>
+      </c>
       <c r="I104" s="9" t="n">
         <v>0</v>
       </c>
@@ -2861,7 +3089,11 @@
       <c r="G105" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="H105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>We ask sometimes, so we know for some</t>
+        </is>
+      </c>
       <c r="I105" s="9" t="n">
         <v>33</v>
       </c>
@@ -2885,7 +3117,11 @@
       <c r="G106" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>We've got a theory, we've never asked</t>
+        </is>
+      </c>
       <c r="I106" s="11" t="n">
         <v>67</v>
       </c>
@@ -2907,7 +3143,11 @@
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr"/>
-      <c r="H107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>No idea</t>
+        </is>
+      </c>
       <c r="I107" s="11" t="n">
         <v>100</v>
       </c>
@@ -2961,7 +3201,11 @@
       <c r="G110" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="8" t="inlineStr"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>More than half</t>
+        </is>
+      </c>
       <c r="I110" s="9" t="n">
         <v>0</v>
       </c>
@@ -2985,7 +3229,11 @@
       <c r="G111" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>25% to 50%</t>
+        </is>
+      </c>
       <c r="I111" s="9" t="n">
         <v>33</v>
       </c>
@@ -3009,7 +3257,11 @@
       <c r="G112" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>10% to 25%</t>
+        </is>
+      </c>
       <c r="I112" s="11" t="n">
         <v>67</v>
       </c>
@@ -3033,7 +3285,11 @@
       <c r="G113" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>Under 10%</t>
+        </is>
+      </c>
       <c r="I113" s="11" t="n">
         <v>100</v>
       </c>
@@ -3103,7 +3359,11 @@
       <c r="G117" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="H117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>Timing, they weren't ready</t>
+        </is>
+      </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
@@ -3127,7 +3387,11 @@
       <c r="G118" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>Price, we were too expensive</t>
+        </is>
+      </c>
       <c r="I118" s="9" t="n">
         <v>33</v>
       </c>
@@ -3151,7 +3415,11 @@
       <c r="G119" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>They went with someone else</t>
+        </is>
+      </c>
       <c r="I119" s="11" t="n">
         <v>67</v>
       </c>
@@ -3175,7 +3443,11 @@
       <c r="G120" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>They did nothing at all, or we don't know</t>
+        </is>
+      </c>
       <c r="I120" s="11" t="n">
         <v>100</v>
       </c>
@@ -3263,7 +3535,11 @@
       <c r="G125" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>Rarely, they just decide</t>
+        </is>
+      </c>
       <c r="I125" s="9" t="n">
         <v>0</v>
       </c>
@@ -3287,7 +3563,11 @@
       <c r="G126" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
       <c r="I126" s="9" t="n">
         <v>33</v>
       </c>
@@ -3311,7 +3591,11 @@
       <c r="G127" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="n">
         <v>67</v>
       </c>
@@ -3335,7 +3619,11 @@
       <c r="G128" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H128" s="8" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>On most quotes</t>
+        </is>
+      </c>
       <c r="I128" s="11" t="n">
         <v>100</v>
       </c>
@@ -3405,7 +3693,11 @@
       <c r="G132" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H132" s="8" t="inlineStr"/>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>Improved</t>
+        </is>
+      </c>
       <c r="I132" s="9" t="n">
         <v>0</v>
       </c>
@@ -3429,7 +3721,11 @@
       <c r="G133" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>About the same</t>
+        </is>
+      </c>
       <c r="I133" s="9" t="n">
         <v>33</v>
       </c>
@@ -3453,7 +3749,11 @@
       <c r="G134" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
       <c r="I134" s="11" t="n">
         <v>67</v>
       </c>
@@ -3477,7 +3777,11 @@
       <c r="G135" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>Dropped sharply</t>
+        </is>
+      </c>
       <c r="I135" s="11" t="n">
         <v>100</v>
       </c>
@@ -3547,7 +3851,11 @@
       <c r="G139" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>There's a price list or packages they can see themselves</t>
+        </is>
+      </c>
       <c r="I139" s="9" t="n">
         <v>0</v>
       </c>
@@ -3571,7 +3879,11 @@
       <c r="G140" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>Standard pricing, but we walk them through it</t>
+        </is>
+      </c>
       <c r="I140" s="9" t="n">
         <v>33</v>
       </c>
@@ -3595,7 +3907,11 @@
       <c r="G141" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="H141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>Every job gets quoted from scratch</t>
+        </is>
+      </c>
       <c r="I141" s="11" t="n">
         <v>67</v>
       </c>
@@ -3619,7 +3935,11 @@
       <c r="G142" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>It depends who's asking</t>
+        </is>
+      </c>
       <c r="I142" s="11" t="n">
         <v>100</v>
       </c>
@@ -3689,7 +4009,11 @@
       <c r="G146" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H146" s="8" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>More than 30</t>
+        </is>
+      </c>
       <c r="I146" s="9" t="n">
         <v>0</v>
       </c>
@@ -3713,7 +4037,11 @@
       <c r="G147" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>11 to 30</t>
+        </is>
+      </c>
       <c r="I147" s="9" t="n">
         <v>33</v>
       </c>
@@ -3737,7 +4065,11 @@
       <c r="G148" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H148" s="8" t="inlineStr"/>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>3 to 10</t>
+        </is>
+      </c>
       <c r="I148" s="11" t="n">
         <v>67</v>
       </c>
@@ -3761,7 +4093,11 @@
       <c r="G149" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H149" s="8" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>0 to 2</t>
+        </is>
+      </c>
       <c r="I149" s="11" t="n">
         <v>100</v>
       </c>
@@ -3849,7 +4185,11 @@
       <c r="G154" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H154" s="8" t="inlineStr"/>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
       <c r="I154" s="9" t="n">
         <v>0</v>
       </c>
@@ -3873,7 +4213,11 @@
       <c r="G155" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H155" s="8" t="inlineStr"/>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
       <c r="I155" s="9" t="n">
         <v>33</v>
       </c>
@@ -3897,7 +4241,11 @@
       <c r="G156" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H156" s="8" t="inlineStr"/>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
       <c r="I156" s="11" t="n">
         <v>67</v>
       </c>
@@ -3921,7 +4269,11 @@
       <c r="G157" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H157" s="8" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>Down sharply</t>
+        </is>
+      </c>
       <c r="I157" s="11" t="n">
         <v>100</v>
       </c>
@@ -3991,7 +4343,11 @@
       <c r="G161" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="H161" s="8" t="inlineStr"/>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
+          <t>No, we'd be well over capacity</t>
+        </is>
+      </c>
       <c r="I161" s="9" t="n">
         <v>0</v>
       </c>
@@ -4015,7 +4371,11 @@
       <c r="G162" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H162" s="8" t="inlineStr"/>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>Yes, with a real stretch</t>
+        </is>
+      </c>
       <c r="I162" s="9" t="n">
         <v>33</v>
       </c>
@@ -4039,7 +4399,11 @@
       <c r="G163" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H163" s="8" t="inlineStr"/>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
+          <t>Yes, with a bit of room to spare</t>
+        </is>
+      </c>
       <c r="I163" s="11" t="n">
         <v>67</v>
       </c>
@@ -4061,7 +4425,11 @@
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr"/>
-      <c r="H164" s="8" t="inlineStr"/>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>Yes, easily, we've got the space now</t>
+        </is>
+      </c>
       <c r="I164" s="11" t="n">
         <v>100</v>
       </c>
@@ -4115,7 +4483,11 @@
       <c r="G167" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H167" s="8" t="inlineStr"/>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>Yes, the same things every week</t>
+        </is>
+      </c>
       <c r="I167" s="9" t="n">
         <v>0</v>
       </c>
@@ -4139,7 +4511,11 @@
       <c r="G168" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H168" s="8" t="inlineStr"/>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>Yes, but it fits around the work</t>
+        </is>
+      </c>
       <c r="I168" s="9" t="n">
         <v>33</v>
       </c>
@@ -4163,7 +4539,11 @@
       <c r="G169" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H169" s="8" t="inlineStr"/>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>On and off, when it goes quiet</t>
+        </is>
+      </c>
       <c r="I169" s="11" t="n">
         <v>67</v>
       </c>
@@ -4185,7 +4565,11 @@
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
-      <c r="H170" s="8" t="inlineStr"/>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>No, it all comes to us</t>
+        </is>
+      </c>
       <c r="I170" s="11" t="n">
         <v>100</v>
       </c>
@@ -4239,7 +4623,11 @@
       <c r="G173" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H173" s="8" t="inlineStr"/>
+      <c r="H173" s="8" t="inlineStr">
+        <is>
+          <t>More than 50%</t>
+        </is>
+      </c>
       <c r="I173" s="9" t="n">
         <v>0</v>
       </c>
@@ -4263,7 +4651,11 @@
       <c r="G174" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H174" s="8" t="inlineStr"/>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
+          <t>30% to 50%</t>
+        </is>
+      </c>
       <c r="I174" s="9" t="n">
         <v>33</v>
       </c>
@@ -4287,7 +4679,11 @@
       <c r="G175" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H175" s="8" t="inlineStr"/>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>15% to 30%</t>
+        </is>
+      </c>
       <c r="I175" s="11" t="n">
         <v>67</v>
       </c>
@@ -4311,7 +4707,11 @@
       <c r="G176" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H176" s="8" t="inlineStr"/>
+      <c r="H176" s="8" t="inlineStr">
+        <is>
+          <t>Under 15%</t>
+        </is>
+      </c>
       <c r="I176" s="11" t="n">
         <v>100</v>
       </c>
@@ -4381,7 +4781,11 @@
       <c r="G180" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H180" s="8" t="inlineStr"/>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
+          <t>More than 20%</t>
+        </is>
+      </c>
       <c r="I180" s="9" t="n">
         <v>0</v>
       </c>
@@ -4405,7 +4809,11 @@
       <c r="G181" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H181" s="8" t="inlineStr"/>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
+          <t>10% to 20%</t>
+        </is>
+      </c>
       <c r="I181" s="9" t="n">
         <v>33</v>
       </c>
@@ -4429,7 +4837,11 @@
       <c r="G182" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H182" s="8" t="inlineStr"/>
+      <c r="H182" s="8" t="inlineStr">
+        <is>
+          <t>1% to 10%</t>
+        </is>
+      </c>
       <c r="I182" s="11" t="n">
         <v>67</v>
       </c>
@@ -4453,7 +4865,11 @@
       <c r="G183" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H183" s="8" t="inlineStr"/>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>Nothing, or a loss</t>
+        </is>
+      </c>
       <c r="I183" s="11" t="n">
         <v>100</v>
       </c>
@@ -4523,7 +4939,11 @@
       <c r="G187" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H187" s="8" t="inlineStr"/>
+      <c r="H187" s="8" t="inlineStr">
+        <is>
+          <t>In the last 6 months</t>
+        </is>
+      </c>
       <c r="I187" s="9" t="n">
         <v>0</v>
       </c>
@@ -4547,7 +4967,11 @@
       <c r="G188" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H188" s="8" t="inlineStr"/>
+      <c r="H188" s="8" t="inlineStr">
+        <is>
+          <t>6 to 12 months ago</t>
+        </is>
+      </c>
       <c r="I188" s="9" t="n">
         <v>33</v>
       </c>
@@ -4571,7 +4995,11 @@
       <c r="G189" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H189" s="8" t="inlineStr"/>
+      <c r="H189" s="8" t="inlineStr">
+        <is>
+          <t>1 to 2 years ago</t>
+        </is>
+      </c>
       <c r="I189" s="11" t="n">
         <v>67</v>
       </c>
@@ -4595,7 +5023,11 @@
       <c r="G190" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="H190" s="8" t="inlineStr"/>
+      <c r="H190" s="8" t="inlineStr">
+        <is>
+          <t>More than 2 years ago, or never</t>
+        </is>
+      </c>
       <c r="I190" s="11" t="n">
         <v>100</v>
       </c>
@@ -4683,7 +5115,11 @@
       <c r="G195" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="8" t="inlineStr"/>
+      <c r="H195" s="8" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
       <c r="I195" s="9" t="n">
         <v>0</v>
       </c>
@@ -4707,7 +5143,11 @@
       <c r="G196" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="H196" s="8" t="inlineStr"/>
+      <c r="H196" s="8" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
       <c r="I196" s="9" t="n">
         <v>33</v>
       </c>
@@ -4731,7 +5171,11 @@
       <c r="G197" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H197" s="8" t="inlineStr"/>
+      <c r="H197" s="8" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
       <c r="I197" s="11" t="n">
         <v>67</v>
       </c>
@@ -4755,7 +5199,11 @@
       <c r="G198" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H198" s="8" t="inlineStr"/>
+      <c r="H198" s="8" t="inlineStr">
+        <is>
+          <t>On most jobs</t>
+        </is>
+      </c>
       <c r="I198" s="11" t="n">
         <v>100</v>
       </c>
@@ -4825,7 +5273,11 @@
       <c r="G202" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H202" s="8" t="inlineStr"/>
+      <c r="H202" s="8" t="inlineStr">
+        <is>
+          <t>Yes, job by job</t>
+        </is>
+      </c>
       <c r="I202" s="9" t="n">
         <v>0</v>
       </c>
@@ -4849,7 +5301,11 @@
       <c r="G203" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="H203" s="8" t="inlineStr"/>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>Yes by category, not job by job</t>
+        </is>
+      </c>
       <c r="I203" s="9" t="n">
         <v>33</v>
       </c>
@@ -4873,7 +5329,11 @@
       <c r="G204" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="H204" s="8" t="inlineStr"/>
+      <c r="H204" s="8" t="inlineStr">
+        <is>
+          <t>Roughly, it's a feel</t>
+        </is>
+      </c>
       <c r="I204" s="11" t="n">
         <v>67</v>
       </c>
@@ -4895,7 +5355,11 @@
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr"/>
-      <c r="H205" s="8" t="inlineStr"/>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I205" s="11" t="n">
         <v>100</v>
       </c>
